--- a/branches/release/v2027.0.0-ballot/ValueSet-mii-vs-lufu-sct-irv-erv.xlsx
+++ b/branches/release/v2027.0.0-ballot/ValueSet-mii-vs-lufu-sct-irv-erv.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc2</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02</t>
+    <t>2026-09-15</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>This value set includes content from SNOMED CT, which is copyright © 2002+ International Health Terminology Standards Development Organisation (IHTSDO), and distributed by agreement between IHTSDO and HL7. Implementer use of SNOMED CT is not covered by this agreement</t>
+    <t>This material includes SNOMED Clinical Terms® (SNOMED CT®) which is used by permission of SNOMED International. All rights reserved. SNOMED CT®, was originally created by The College of American Pathologists. SNOMED and SNOMED CT are registered trademarks of SNOMED International. Implementers of these artefacts must have the appropriate SNOMED CT Affiliate license.</t>
   </si>
   <si>
     <t>Immutable</t>
